--- a/src/test/resources/farmer-import/Plantilla_listado_de_agricultores_otros_paises_es.xlsx
+++ b/src/test/resources/farmer-import/Plantilla_listado_de_agricultores_otros_paises_es.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="566">
   <si>
     <t>Caserio</t>
   </si>
@@ -1693,6 +1693,33 @@
   </si>
   <si>
     <t>8. La columna de datos geográficos tiene el formato: POLYGON((lat_1 lon_1, lat_2 lon_2, ...))</t>
+  </si>
+  <si>
+    <t>Datos geográficos (POLYGON((lat1 lon1, lat2 lon2,...)), POINT(lat lon), GeoJSON, geoshape de ODK/Kobo "lat lon alt prec;...", o P1(...)P2(...) para varias parcelas)</t>
+  </si>
+  <si>
+    <t>GeoID (FAO) - identificador del límite de la parcela en el registro GeoID de la FAO</t>
+  </si>
+  <si>
+    <t>8. La columna de datos geográficos acepta cualquiera de estos formatos: utilice el que haya generado su GPS, SIG o herramienta de recogida de datos, no hace falta convertirlo a mano:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a) Polígono o punto WKT, como se documentaba antes: POLYGON((lat_1 lon_1, lat_2 lon_2, ...)) o POINT(lat lon). También se admite el WKT estándar lon/lat de QGIS o PostGIS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    b) Geoshape, geotrace o geopoint de ODK / KoboToolbox, copiado directamente de la exportación: 5.1717367 10.2352433 1267.1 1.45;5.1718067 10.235235 1267.8 1.3;...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    c) GeoJSON: {"type":"Polygon","coordinates":[[[10.235,5.171],[10.236,5.172],[10.237,5.173],[10.235,5.171]]]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    d) Varias parcelas para un mismo agricultor: P1(&lt;datos geográficos&gt;)P2(&lt;datos geográficos&gt;), usando cualquiera de los formatos anteriores dentro de cada paréntesis.</t>
+  </si>
+  <si>
+    <t>9. Un agricultor con varias parcelas también puede ocupar varias filas: rellene las columnas del agricultor una sola vez y ponga cada parcela adicional en su propia fila, dejando vacías todas las demás columnas.</t>
+  </si>
+  <si>
+    <t>10. La columna GeoID admite el identificador de un límite de parcela ya registrado en la FAO (https://data.apps.fao.org/geoid). El límite se obtiene del registro, por lo que no hacen falta coordenadas. Si se rellenan ambas columnas, se usa el GeoID y las coordenadas sirven de reserva si no se puede contactar con el registro.</t>
   </si>
 </sst>
 </file>
@@ -3233,7 +3260,7 @@
   <dimension ref="A1:AM260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="35" max="40" customWidth="true" style="1" width="8.6640625"/>
+    <col min="36" max="40" customWidth="true" style="1" width="8.6640625"/>
     <col min="1" max="1" customWidth="true" style="1" width="25.33203125"/>
     <col min="2" max="2" customWidth="true" style="1" width="23.33203125"/>
     <col min="3" max="3" customWidth="true" style="1" width="32.5"/>
@@ -3256,6 +3283,7 @@
     <col min="32" max="32" customWidth="true" style="1" width="25.5"/>
     <col min="33" max="33" customWidth="true" style="1" width="22.6640625"/>
     <col min="34" max="34" customWidth="true" style="1" width="29.5703125"/>
+    <col min="35" max="35" customWidth="true" style="1" width="29.5703125"/>
     <col min="41" max="16384" style="1" width="8.6640625"/>
   </cols>
   <sheetData>
@@ -3526,9 +3554,11 @@
         <v>23</v>
       </c>
       <c r="AH5" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="AI5" s="3"/>
+        <v>557</v>
+      </c>
+      <c r="AI5" s="24" t="s">
+        <v>558</v>
+      </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
@@ -14003,7 +14033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5EF26B-2F8C-7342-8679-249E4BD9A902}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="29" width="169.5"/>
@@ -14052,7 +14082,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="29">
-        <v>556</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
